--- a/data/processed/ontology/labor/predicate_lexicon.xlsx
+++ b/data/processed/ontology/labor/predicate_lexicon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,32 +503,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRED_UY_QUYEN_BANG_VAN_BAN</t>
+          <t>PRED_THANH_PHAN_HO_SO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ủy quyền để thực hiện quyền, trách nhiệm của đại diện chủ sở hữu nhà nước</t>
+          <t>thành phần hồ sơ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ủy quyền để thực hiện quyền, trách nhiệm của đại diện chủ sở hữu nhà nước</t>
+          <t>thành phần hồ sơ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yeu_cau_bao_cao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>uy_quyen_bang_van_ban</t>
+          <t>thanh_phan_ho_so</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>uy_quyen_va_lay_y_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>phần vốn nhà nước tại doanh nghiệp</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -564,24 +564,24 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_uy_quyen_bang_van_ban</t>
+          <t>map_khi_thay_cum_thanh_phan_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRED_THANH_PHAN_HO_SO</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>thành phần hồ sơ</t>
+          <t>kèm theo Nghị định này.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thành phần hồ sơ</t>
+          <t>kèm theo Nghị định này.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>thanh_phan_ho_so</t>
+          <t>kem_theo_nghi_dinh_nay</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -604,11 +604,7 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ho_so</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -632,24 +628,24 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thanh_phan_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY</t>
+          <t>PRED_KEM_THEO_QUYET_DINH_CUA_CHU_TICH_UY_BAN_NHAN_DAN_CAP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này.</t>
+          <t>kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này.</t>
+          <t>kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi | kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -659,7 +655,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>kem_theo_nghi_dinh_nay</t>
+          <t>kem_theo_quyet_dinh_cua_chu_tich_uy_ban_nhan_dan_cap_tinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -673,10 +669,14 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -703,32 +703,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_QUYET_DINH_CUA_CHU_TICH_UY_BAN_NHAN_DAN_CAP</t>
+          <t>PRED_THU_HOI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi</t>
+          <t>thu hồi giấy phép trong các</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi | kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>thu hồi giấy phép trong các</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>kem_theo_quyet_dinh_cua_chu_tich_uy_ban_nhan_dan_cap_tinh</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -736,20 +736,20 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,44 +759,44 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_thu_hoi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRED_THU_HOI</t>
+          <t>PRED_CAP_GIAY_PHEP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>thu hồi giấy phép trong các</t>
+          <t>cấp giấy phép</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thu hồi giấy phép trong các</t>
+          <t>cấp giấy phép | cấp giấy phép với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay_phep</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -806,13 +806,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>trường hợp sau đây:</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -827,44 +831,44 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thu_hoi</t>
+          <t>map_khi_thay_cum_cap_giay_phep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRED_CAP_GIAY_PHEP</t>
+          <t>PRED_KEM_THEO_NOI_QUY_LAO_DONG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cấp giấy phép</t>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cấp giấy phép | cấp giấy phép với cơ quan đăng ký kinh doanh</t>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>cap_giay_phep</t>
+          <t>kem_theo_noi_quy_lao_dong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -872,26 +876,18 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>thời hạn 05 năm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>co</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>khong</t>
@@ -899,29 +895,29 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_giay_phep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NOI_QUY_LAO_DONG</t>
+          <t>PRED_DANH_SACH_NGUOI_LAO_DONG_THAM_GIA_BAO_HIEM_XA_HOI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -931,7 +927,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>kem_theo_noi_quy_lao_dong</t>
+          <t>danh_sach_nguoi_lao_dong_tham_gia_bao_hiem_xa_hoi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -944,7 +940,11 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>danh sách</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -975,17 +975,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRED_DANH_SACH_NGUOI_LAO_DONG_THAM_GIA_BAO_HIEM_XA_HOI</t>
+          <t>PRED_DANH_SACH_LAO_DONG_TAI_THOI_DIEM_TRUOC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+          <t>danh sách lao động tại thời điểm trước</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+          <t>danh sách lao động tại thời điểm trước</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>danh_sach_nguoi_lao_dong_tham_gia_bao_hiem_xa_hoi</t>
+          <t>danh_sach_lao_dong_tai_thoi_diem_truoc</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1008,11 +1008,7 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>danh sách</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -1031,74 +1027,10 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
-        <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PRED_DANH_SACH_LAO_DONG_TAI_THOI_DIEM_TRUOC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>danh sách lao động tại thời điểm trước</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>danh sách lao động tại thời điểm trước</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>danh_sach_lao_dong_tai_thoi_diem_truoc</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
         <is>
           <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>

--- a/data/processed/ontology/labor/predicate_lexicon.xlsx
+++ b/data/processed/ontology/labor/predicate_lexicon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,32 +635,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_QUYET_DINH_CUA_CHU_TICH_UY_BAN_NHAN_DAN_CAP</t>
+          <t>PRED_THU_HOI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi</t>
+          <t>thu hồi giấy phép trong các</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi | kèm theo quyết định của Chủ tịch Ủy ban nhân dân cấp tỉnh, sau khi trừ chi phí dịch vụ ngân hàng. Tiền ký quỹ của doanh nghiệp cho thuê được thanh toán theo thứ tự ưu tiên: tiền lương; bảo hiểm xã hội, bảo hiểm y tế, bảo hiểm thất nghiệp; bảo hiểm tai nạn lao động, bệnh nghề nghi với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>thu hồi giấy phép trong các</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>kem_theo_quyet_dinh_cua_chu_tich_uy_ban_nhan_dan_cap_tinh</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,20 +668,20 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -691,44 +691,44 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_thu_hoi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRED_THU_HOI</t>
+          <t>PRED_CAP_GIAY_PHEP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>thu hồi giấy phép trong các</t>
+          <t>cấp giấy phép</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>thu hồi giấy phép trong các</t>
+          <t>cấp giấy phép | cấp giấy phép với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay_phep</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -738,13 +738,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>trường hợp sau đây:</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -759,44 +763,44 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thu_hoi</t>
+          <t>map_khi_thay_cum_cap_giay_phep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRED_CAP_GIAY_PHEP</t>
+          <t>PRED_KEM_THEO_NOI_QUY_LAO_DONG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cấp giấy phép</t>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cấp giấy phép | cấp giấy phép với cơ quan đăng ký kinh doanh</t>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cap_giay_phep</t>
+          <t>kem_theo_noi_quy_lao_dong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -804,26 +808,18 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>thời hạn 05 năm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>co</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>khong</t>
@@ -831,29 +827,29 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_giay_phep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NOI_QUY_LAO_DONG</t>
+          <t>PRED_DANH_SACH_NGUOI_LAO_DONG_THAM_GIA_BAO_HIEM_XA_HOI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội | danh sách người lao động tham gia bảo hiểm xã hội với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -863,7 +859,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>kem_theo_noi_quy_lao_dong</t>
+          <t>danh_sach_nguoi_lao_dong_tham_gia_bao_hiem_xa_hoi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -876,8 +872,16 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>danh sách</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>khong</t>
@@ -907,17 +911,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRED_DANH_SACH_NGUOI_LAO_DONG_THAM_GIA_BAO_HIEM_XA_HOI</t>
+          <t>PRED_DANH_SACH_LAO_DONG_TAI_THOI_DIEM_TRUOC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+          <t>danh sách lao động tại thời điểm trước</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+          <t>danh sách lao động tại thời điểm trước</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -927,7 +931,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>danh_sach_nguoi_lao_dong_tham_gia_bao_hiem_xa_hoi</t>
+          <t>danh_sach_lao_dong_tai_thoi_diem_truoc</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -940,11 +944,7 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>danh sách</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -975,41 +975,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRED_DANH_SACH_LAO_DONG_TAI_THOI_DIEM_TRUOC</t>
+          <t>PRED_THONG_BAO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>danh sách lao động tại thời điểm trước</t>
+          <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>danh sách lao động tại thời điểm trước</t>
+          <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể | Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>danh_sach_lao_dong_tai_thoi_diem_truoc</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>thủ tục</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1017,7 +1025,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,12 +1035,84 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_thong_bao;khong_dong_nhat_voi_cong_bo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRED_CUA_CO_QUAN_DANG_KY_KINH_DOANH_VE_VIEC_DOANH_NGHIEP_</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể | của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể với cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dang_ky</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>cua_co_quan_dang_ky_kinh_doanh_ve_viec_doanh_nghiep_dang_lam_thu_tuc_giai_the</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>dang_ky</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>map_khi_thay_cum_cua_co_quan_dang_ky_kinh_doanh_ve_viec_doanh_nghiep_dang_lam_thu_tuc_giai_the;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
